--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="D2">
-        <v>185</v>
+        <v>332</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="D3">
-        <v>225</v>
+        <v>310</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D3">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E3">
         <v>0</v>
